--- a/plantillas/encuestas/plantilla-encuesta-mdeia-autoridad.xlsx
+++ b/plantillas/encuestas/plantilla-encuesta-mdeia-autoridad.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -521,142 +521,154 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>META_CARGO</t>
+          <t>Unidades MDeIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cargo o rol institucional [texto]</t>
+          <t>Departamento Administrativo Sede San Juan; Departamento Administrativo Sede San Luis; ECRyPSJ- Escuela de Cultura Religiosa y Pastoral Sede San Juan; ESEGSJ- Escuela de Seguridad Sede San Juan; FBOSCO- Facultad Don Bosco Sede Mendoza; FCEESJ- Facultad de Ciencias Económicas y Empresariales Sede San Juan; FCEESL- Facultad de Ciencias Económicas y Empresariales Sede San Luis; FCMSJ- Facultad de Ciencias Médicas Sede San Juan; FCMSL- Facultad de Ciencias Médicas Sede San Luis; FCQyTSJ- Facultad de Ciencias Químicas y Tecnológicas Sede San Juan; FCVSL- Facultad de Ciencias Veterinarias Sede San Luis; FDCSSJ- Facultad de Derecho y Ciencias Sociales Sede San Juan; FDCSSL- Facultad de Derecho y Ciencias Sociales Sede San Luis; FFyHSJ- Facultad de Filosofía y Humanidades Sede San Juan; ISB- Instituto de Formación Docente San Buenaventura Sede San Juan; ISDSM- Instituto de Formación Docente Santa María Sede San Juan; OIA- Observatorio de Inteligencia Artificial; Secretaría de Extensión; Secretaría de Investigación; UCCuyo — Universidad Católica de Cuyo (institución completa)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>META_SEDE</t>
+          <t>META_CARGO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ámbito de evaluación [meta_sede]</t>
+          <t>Cargo o rol institucional [texto]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IND_ESTRATEGIA_DIGITAL</t>
+          <t>META_SEDE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>¿En qué nivel la institución dispone de estrategia digital alineada con la estrategia institucional? [madurez]</t>
+          <t>Ámbito de evaluación [meta_sede]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IND_ESTRATEGIA_UNI</t>
+          <t>IND_ESTRATEGIA_DIGITAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>¿En qué nivel existe estrategia de negocio institucional formalmente definida? [madurez]</t>
+          <t>¿En qué nivel la institución dispone de estrategia digital alineada con la estrategia institucional? [madurez]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IND_LIDERAZGO_RECTOR</t>
+          <t>IND_ESTRATEGIA_UNI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>¿En qué nivel el Rectorado y equipo de gobierno lideran la planificación estratégica de TI y transformación digital? [madurez]</t>
+          <t>¿En qué nivel existe estrategia de negocio institucional formalmente definida? [madurez]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IND_PLAN_TD</t>
+          <t>IND_LIDERAZGO_RECTOR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>¿En qué nivel existe un Plan de Transformación Digital aprobado por el equipo de gobierno? [madurez]</t>
+          <t>¿En qué nivel el Rectorado y equipo de gobierno lideran la planificación estratégica de TI y transformación digital? [madurez]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IND_MODELO_GOBIERNO_TI</t>
+          <t>IND_PLAN_TD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>¿En qué nivel está implementado el modelo de gobierno de TI (roles, comités, políticas)? [madurez]</t>
+          <t>¿En qué nivel existe un Plan de Transformación Digital aprobado por el equipo de gobierno? [madurez]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IND_COMISION_ESTRATEGIA_TI</t>
+          <t>IND_MODELO_GOBIERNO_TI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>¿En qué nivel funciona un comité de estrategia y gobierno de TI? [madurez]</t>
+          <t>¿En qué nivel está implementado el modelo de gobierno de TI (roles, comités, políticas)? [madurez]</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IND_PLAN_FINANCIACION_TI</t>
+          <t>IND_COMISION_ESTRATEGIA_TI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>¿En qué nivel existe plan de financiación plurianual de TI alineado con la estrategia? [madurez]</t>
+          <t>¿En qué nivel funciona un comité de estrategia y gobierno de TI? [madurez]</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IND_GUIA_ETICA_IA</t>
+          <t>IND_PLAN_FINANCIACION_TI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>¿En qué nivel está aprobada e implementada la guía de uso responsable de IA generativa? [madurez]</t>
+          <t>¿En qué nivel existe plan de financiación plurianual de TI alineado con la estrategia? [madurez]</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IND_ENCUESTA_IA_PERIODICA</t>
+          <t>IND_GUIA_ETICA_IA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>¿En qué nivel la institución realiza encuestas periódicas sobre uso de IA en la comunidad? [madurez]</t>
+          <t>¿En qué nivel está aprobada e implementada la guía de uso responsable de IA generativa? [madurez]</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>IND_ENCUESTA_IA_PERIODICA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>¿En qué nivel la institución realiza encuestas periódicas sobre uso de IA en la comunidad? [madurez]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>IND_OBSERVATORIO_IA</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>¿En qué nivel está activo un observatorio o instancia de monitoreo de IA institucional? [madurez]</t>
         </is>
